--- a/results/02_taxa_assemblage/tables/anova_env.xlsx
+++ b/results/02_taxa_assemblage/tables/anova_env.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,11 +474,6 @@
           <t>Cluster C2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster C3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -490,19 +485,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.43</v>
+        <v>24.07</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>17.3</v>
+        <v>17.66</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>30.35</v>
+        <v>59.95</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +506,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.35 ± 0.12</t>
+          <t>1.39 ± 0.10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>-1.17 ± 0.08</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1.60 ± 0.14</t>
         </is>
       </c>
     </row>
@@ -531,42 +521,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Measured Depth (m)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.34</v>
+        <v>0.31</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>181.33</v>
+        <v>12.25</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>3.36</v>
+        <v>1.12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0441*</t>
+          <t>0.2961</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.74 ± 0.34</t>
+          <t>1.26 ± 0.08</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.10 ± 0.84</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>4.79 ± 0.94</t>
+          <t>1.55 ± 0.18</t>
         </is>
       </c>
     </row>
@@ -576,42 +561,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>Measured Depth (m)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.54</v>
+        <v>3.82</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>23.44</v>
+        <v>205.84</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>1.41</v>
+        <v>0.82</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.2548</t>
+          <t>0.3709</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9.64 ± 0.11</t>
+          <t>3.08 ± 0.34</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.53 ± 0.25</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>9.13 ± 0.44</t>
+          <t>4.10 ± 0.84</t>
         </is>
       </c>
     </row>
@@ -621,42 +601,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15.01</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>235.66</v>
+        <v>24.97</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.2651</t>
+          <t>0.9445</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>19.64 ± 0.44</t>
+          <t>9.56 ± 0.12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19.94 ± 0.26</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>21.25 ± 0.31</t>
+          <t>9.53 ± 0.25</t>
         </is>
       </c>
     </row>
@@ -666,42 +641,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>11.93</v>
+        <v>250.67</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.9828</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.22 ± 0.08</t>
+          <t>19.91 ± 0.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.55 ± 0.18</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>1.45 ± 0.28</t>
+          <t>19.94 ± 0.26</t>
         </is>
       </c>
     </row>
@@ -718,7 +688,6 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -736,13 +705,10 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -758,7 +724,6 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -777,7 +742,6 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/02_taxa_assemblage/tables/anova_env.xlsx
+++ b/results/02_taxa_assemblage/tables/anova_env.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>Cluster C2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster C3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -481,23 +486,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MPS (Phi)</t>
+          <t>Measured Depth (m)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.07</v>
+        <v>312.67</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>17.66</v>
+        <v>346.13</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>59.95</v>
+        <v>19.42</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -506,12 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.39 ± 0.10</t>
+          <t>3.64 ± 0.61</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.17 ± 0.08</t>
+          <t>9.35 ± 0.98</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3.12 ± 0.57</t>
         </is>
       </c>
     </row>
@@ -521,37 +531,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>MPS (Phi)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.31</v>
+        <v>3.95</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>12.25</v>
+        <v>17.61</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>1.12</v>
+        <v>4.83</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.2961</t>
+          <t>0.0128*</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.26 ± 0.08</t>
+          <t>1.28 ± 0.12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.55 ± 0.18</t>
+          <t>0.67 ± 0.25</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.38 ± 0.12</t>
         </is>
       </c>
     </row>
@@ -561,37 +576,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Measured Depth (m)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.82</v>
+        <v>35.55</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>205.84</v>
+        <v>234.32</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>0.82</v>
+        <v>3.26</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.3709</t>
+          <t>0.0480*</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.08 ± 0.34</t>
+          <t>20.78 ± 0.32</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.10 ± 0.84</t>
+          <t>18.13 ± 0.72</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>19.60 ± 0.51</t>
         </is>
       </c>
     </row>
@@ -605,33 +625,38 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>24.97</v>
+        <v>115.12</v>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.9445</t>
+          <t>0.6587</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9.56 ± 0.12</t>
+          <t>9.60 ± 0.37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.53 ± 0.25</t>
+          <t>8.94 ± 0.61</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>9.32 ± 0.32</t>
         </is>
       </c>
     </row>
@@ -641,37 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>250.67</v>
+        <v>120.15</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.9828</t>
+          <t>0.9334</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>19.91 ± 0.38</t>
+          <t>1.83 ± 0.60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19.94 ± 0.26</t>
+          <t>2.06 ± 0.42</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2.06 ± 0.34</t>
         </is>
       </c>
     </row>
@@ -688,6 +718,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -705,10 +736,13 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="K8" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -724,6 +758,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -742,6 +777,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
